--- a/file/Azure_Managed_HSM_VPATJ02210.xlsx
+++ b/file/Azure_Managed_HSM_VPATJ02210.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CDD8308-0DEA-429B-886D-39AB725DB8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9CC532F-191F-4C47-867D-E5A42C059727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{8AD22F91-DBF8-4473-99E7-F39342F87EA5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{30DE5F36-7621-4E1E-933A-D8A511E3B09E}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -65,7 +65,7 @@
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2026年10月1日</t>
+    <t>作成日：2025年10月15日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -2017,7 +2017,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9558B06-91D0-4ED7-91EE-63236105F19C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{200FC44D-440C-4603-B223-47866EFDC8E1}">
   <sheetPr codeName="Sheet240">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2073,7 +2073,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -2090,7 +2090,7 @@
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="13"/>
       <c r="B5" s="14"/>
       <c r="C5" s="15"/>
@@ -2116,7 +2116,7 @@
       <c r="H6" s="17"/>
       <c r="I6" s="18"/>
     </row>
-    <row r="7" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="13"/>
       <c r="B7" s="14"/>
       <c r="C7" s="15"/>
@@ -2127,7 +2127,7 @@
       <c r="H7" s="17"/>
       <c r="I7" s="18"/>
     </row>
-    <row r="8" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
@@ -2140,7 +2140,7 @@
       <c r="H8" s="17"/>
       <c r="I8" s="18"/>
     </row>
-    <row r="9" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="13"/>
       <c r="B9" s="14"/>
       <c r="C9" s="15"/>
@@ -2166,7 +2166,7 @@
       <c r="H10" s="17"/>
       <c r="I10" s="18"/>
     </row>
-    <row r="11" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="13"/>
       <c r="B11" s="14"/>
       <c r="C11" s="15"/>
@@ -2177,7 +2177,7 @@
       <c r="H11" s="17"/>
       <c r="I11" s="18"/>
     </row>
-    <row r="12" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="6" t="s">
         <v>10</v>
       </c>
@@ -2192,7 +2192,7 @@
       <c r="H12" s="17"/>
       <c r="I12" s="18"/>
     </row>
-    <row r="13" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="13"/>
       <c r="B13" s="14"/>
       <c r="C13" s="15"/>
@@ -2203,7 +2203,7 @@
       <c r="H13" s="17"/>
       <c r="I13" s="18"/>
     </row>
-    <row r="14" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="6" t="s">
         <v>12</v>
       </c>
@@ -2833,7 +2833,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{4BE0E6D5-5140-4D76-BE32-B0871B57AD05}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{40A662E6-D940-4E11-BEC7-44324EA07BD7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -2841,7 +2841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4AA949-5696-4098-A55A-F3493299FDA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B2E27E-EC57-46B1-972A-78F03B0702E8}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
